--- a/food_beverage_order_forms/046_rsvp_with_meal_choice_template--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/046_rsvp_with_meal_choice_template--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meal</t>
+          <t>Guest 2 Meal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Meal</t>
+          <t>Guest 3 Meal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
